--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.9%</t>
+          <t>-687.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.25304625554782</v>
+        <v>-5.253915475600787</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9423610326095688</v>
+        <v>0.9420133445883816</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4986596304067379</v>
+        <v>-0.4995314652532757</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.744740180898401</v>
+        <v>2.744217079990479</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>452.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.0%</t>
+          <t>-687.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.0%</t>
+          <t>-282.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.9%</t>
+          <t>-273.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-171.1%</t>
         </is>
       </c>
     </row>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.230150153767569</v>
+        <v>-5.256621496981142</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8870453847056705</v>
+        <v>0.8764568474202417</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6204392541527666</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.0706350502482</v>
+        <v>-5.097106393461773</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9519972705537203</v>
+        <v>0.9414087332682914</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4609241506333966</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.925962905148462</v>
+        <v>-4.952434248362035</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.019954231155055</v>
+        <v>1.009365693869626</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3162520055336592</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.985837732506154</v>
+        <v>-5.012309075719728</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9820417916134043</v>
+        <v>0.971453254327975</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3761268328913513</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.899038234727145</v>
+        <v>-4.925509577940719</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.039162084047574</v>
+        <v>1.028573546762144</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3761268328913513</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.901507941188951</v>
+        <v>-4.927979284402525</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.038246602836264</v>
+        <v>1.027658065550834</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3785965393531575</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.969878127512962</v>
+        <v>-4.996349470726535</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.021905450781362</v>
+        <v>1.011316913495932</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3693208403169426</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.078416308429095</v>
+        <v>-5.104887651642669</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9689268870467993</v>
+        <v>0.95833834976137</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3693208403169426</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.109409467757801</v>
+        <v>-5.135880810971375</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7812391883557042</v>
+        <v>0.7706506510702744</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3693208403169426</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.933935207965332</v>
+        <v>-4.960406551178906</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8559961242644794</v>
+        <v>0.8454075869790498</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3693208403169426</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.044871460606581</v>
+        <v>-5.071342803820155</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7873636519691867</v>
+        <v>0.7767751146837574</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3693208403169426</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.053153534751639</v>
+        <v>-5.079624877965213</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7871822075310688</v>
+        <v>0.7765936702456395</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3776029144620009</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.895227935816346</v>
+        <v>-4.92169927902992</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8605248335373186</v>
+        <v>0.849936296251889</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3776029144620009</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.808984472789969</v>
+        <v>-4.835455816003543</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8899684893217299</v>
+        <v>0.8793799520363004</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3776029144620009</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.854291292188949</v>
+        <v>-4.880762635402522</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8636215370066636</v>
+        <v>0.853032999721234</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4184130774712317</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.88332439689125</v>
+        <v>-4.909795740104824</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8525601681588446</v>
+        <v>0.8419716308734151</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4184130774712317</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.79051391544039</v>
+        <v>-4.816985258653964</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8189570526305543</v>
+        <v>0.8083685153451245</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3256025960203724</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.834903384769818</v>
+        <v>-4.861374727983391</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.803074740823384</v>
+        <v>0.7924862035379545</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3699920653498001</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.722232166533567</v>
+        <v>-4.748703509747141</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.843218936629607</v>
+        <v>0.8326303993441775</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2573208471135499</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.609855165350894</v>
+        <v>-4.636326508564468</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8936610329333434</v>
+        <v>0.8830724956479139</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2573208471135499</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.808089734237625</v>
+        <v>-4.834561077451199</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8258644071471903</v>
+        <v>0.8152758698617606</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4555554160002804</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.891091015262904</v>
+        <v>-4.917562358476478</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.631019614737732</v>
+        <v>0.6204310774523023</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4741263005274542</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.999705093706235</v>
+        <v>-5.026176436919809</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7077236440796051</v>
+        <v>0.6971351067941756</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4741263005274542</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.086303676687338</v>
+        <v>-5.112775019900912</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6875972369894869</v>
+        <v>0.6770086997040572</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4741263005274542</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.047920014129187</v>
+        <v>-5.074391357342761</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7003701433551162</v>
+        <v>0.6897816060696864</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.435742637969303</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.870803684094021</v>
+        <v>-4.897275027307595</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7679457042144844</v>
+        <v>0.7573571669290549</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.435742637969303</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.915895928927567</v>
+        <v>-4.942367272141141</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7505921980429793</v>
+        <v>0.7400036607575498</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4976386811386928</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.736520507688799</v>
+        <v>-4.762991850902373</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8161293418449007</v>
+        <v>0.8055408045594712</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3408619229679741</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.781534721209406</v>
+        <v>-4.80800606442298</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7789311117682478</v>
+        <v>0.7683425744828183</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3712108182825787</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.048539231481841</v>
+        <v>-5.075010574695415</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6778208699982193</v>
+        <v>0.66723233271279</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5655738563255273</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.149737012919013</v>
+        <v>-5.176208356132587</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6365456793198518</v>
+        <v>0.6259571420344221</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6339826698708464</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.117261426748241</v>
+        <v>-5.143732769961815</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6471358753424776</v>
+        <v>0.6365473380570479</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6339826698708464</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.098223299040944</v>
+        <v>-5.124694642254518</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6512758456336414</v>
+        <v>0.6406873083482116</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.6921662812020409</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.129349930191562</v>
+        <v>-5.155821273405136</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8164070621120745</v>
+        <v>0.8058185248266447</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.6921662812020409</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.181670310792354</v>
+        <v>-5.208141654005928</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7963122388578912</v>
+        <v>0.7857237015724619</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6572194211931688</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.201927609321312</v>
+        <v>-5.228398952534886</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7942178498432342</v>
+        <v>0.7836293125578044</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6572194211931688</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.054184639086309</v>
+        <v>-5.080655982299883</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9324676857292569</v>
+        <v>0.9218791484438276</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.4894120639582856</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.156199321617531</v>
+        <v>-5.182670664831105</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8944554342482496</v>
+        <v>0.8838668969628198</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.4894120639582856</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.150046615564746</v>
+        <v>-5.17651795877832</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8975788650610217</v>
+        <v>0.8869903277755919</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.4832593579055013</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.292811948387397</v>
+        <v>-5.31928329160097</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8395532086720716</v>
+        <v>0.8289646713866423</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.6260246907281517</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.230513949611274</v>
+        <v>-5.256985292824848</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9308079619793417</v>
+        <v>0.9202194246939119</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.6260246907281517</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.028723751946116</v>
+        <v>-5.05519509515969</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.720104913434803</v>
+        <v>0.7095163761493732</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.4280064985589973</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.968833070303523</v>
+        <v>-4.995304413517097</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8143514184140153</v>
+        <v>0.8037628811285857</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.3681158169164038</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.066573614928497</v>
+        <v>-5.093044958142071</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.789882936680069</v>
+        <v>0.7792943993946397</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.384005095049384</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.242911375051427</v>
+        <v>-5.269382718265001</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7178838134555692</v>
+        <v>0.7072952761701394</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.5603428551723134</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.242222002890204</v>
+        <v>-5.268693346103777</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7166511803599871</v>
+        <v>0.7060626430745574</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.5603428551723134</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.248792967944796</v>
+        <v>-5.27526431115837</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.713885661773586</v>
+        <v>0.7032971244881567</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.5669138202269064</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.240838997650024</v>
+        <v>-5.267310340863598</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7170672498914952</v>
+        <v>0.7064787126060654</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.5669138202269064</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.230465621316937</v>
+        <v>-5.256936964530511</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7275983574525342</v>
+        <v>0.7170098201671049</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.5565404438938191</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.102781311522641</v>
+        <v>-5.129252654736215</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7835644547449778</v>
+        <v>0.7729759174595481</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.4288561340995226</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.16344790192503</v>
+        <v>-5.189919245138604</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7460524910598942</v>
+        <v>0.7354639537744645</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.5105544508180563</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.098454041991385</v>
+        <v>-5.124925385204959</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7761477376439809</v>
+        <v>0.7655592003585512</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.4837238362139009</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.199212677748383</v>
+        <v>-5.225684020961957</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7400052229722598</v>
+        <v>0.72941668568683</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.5725494049409063</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.155009840662482</v>
+        <v>-5.181481183876056</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7635659603344571</v>
+        <v>0.7529774230490274</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.5283465678550059</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.191988868325925</v>
+        <v>-5.218460211539499</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7471843497383275</v>
+        <v>0.7365958124528977</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.4913726660636754</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.212046947190766</v>
+        <v>-5.23851829040434</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7904088833754308</v>
+        <v>0.7798203460900015</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.4913726660636754</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.172116274012875</v>
+        <v>-5.198587617226449</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8048218572408401</v>
+        <v>0.7942333199554108</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.451441992885785</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.131645926450171</v>
+        <v>-5.158117269663745</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8159582245041923</v>
+        <v>0.8053696872187626</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.4109716453230801</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.066421745322965</v>
+        <v>-5.092893088536539</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8592353010477791</v>
+        <v>0.8486467637623498</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.3457474641958744</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.116916035680021</v>
+        <v>-5.143387378893595</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8349985572042371</v>
+        <v>0.8244100199188074</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.3907682013219487</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.13702769171473</v>
+        <v>-5.163499034928304</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8282106871215942</v>
+        <v>0.8176221498361644</v>
       </c>
       <c r="F1990" t="n">
         <v>-0.3797408563245295</v>
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.838487471917951</v>
+        <v>3.751262635249041</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.253915475600787</v>
+        <v>-5.26117961420095</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9420133445883816</v>
+        <v>0.9391076891483165</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4995314652532757</v>
+        <v>-0.4904440516647183</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.744217079990479</v>
+        <v>2.749669528143613</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.4%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.7%</t>
+          <t>-681.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.3%</t>
+          <t>-280.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.0%</t>
+          <t>-273.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.1%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.256621496981142</v>
+        <v>-5.230150153767569</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8764568474202417</v>
+        <v>0.8870453847056705</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6204392541527666</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.097106393461773</v>
+        <v>-5.0706350502482</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9414087332682914</v>
+        <v>0.9519972705537203</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4609241506333966</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.952434248362035</v>
+        <v>-4.925962905148462</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.009365693869626</v>
+        <v>1.019954231155055</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3162520055336592</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.012309075719728</v>
+        <v>-4.985837732506154</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.971453254327975</v>
+        <v>0.9820417916134043</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3761268328913513</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.925509577940719</v>
+        <v>-4.899038234727145</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.028573546762144</v>
+        <v>1.039162084047574</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3761268328913513</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.927979284402525</v>
+        <v>-4.901507941188951</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.027658065550834</v>
+        <v>1.038246602836264</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3785965393531575</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.996349470726535</v>
+        <v>-4.969878127512962</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.011316913495932</v>
+        <v>1.021905450781362</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3693208403169426</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.104887651642669</v>
+        <v>-5.078416308429095</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.95833834976137</v>
+        <v>0.9689268870467993</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3693208403169426</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.135880810971375</v>
+        <v>-5.109409467757801</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7706506510702744</v>
+        <v>0.7812391883557042</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3693208403169426</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.960406551178906</v>
+        <v>-4.933935207965332</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8454075869790498</v>
+        <v>0.8559961242644794</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3693208403169426</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.071342803820155</v>
+        <v>-5.044871460606581</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7767751146837574</v>
+        <v>0.7873636519691867</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3693208403169426</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.079624877965213</v>
+        <v>-5.053153534751639</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7765936702456395</v>
+        <v>0.7871822075310688</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3776029144620009</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.92169927902992</v>
+        <v>-4.895227935816346</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.849936296251889</v>
+        <v>0.8605248335373186</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3776029144620009</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.835455816003543</v>
+        <v>-4.808984472789969</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8793799520363004</v>
+        <v>0.8899684893217299</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3776029144620009</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.880762635402522</v>
+        <v>-4.854291292188949</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.853032999721234</v>
+        <v>0.8636215370066636</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4184130774712317</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.909795740104824</v>
+        <v>-4.88332439689125</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8419716308734151</v>
+        <v>0.8525601681588446</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4184130774712317</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.816985258653964</v>
+        <v>-4.79051391544039</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8083685153451245</v>
+        <v>0.8189570526305543</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3256025960203724</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.861374727983391</v>
+        <v>-4.834903384769818</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7924862035379545</v>
+        <v>0.803074740823384</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3699920653498001</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.748703509747141</v>
+        <v>-4.722232166533567</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8326303993441775</v>
+        <v>0.843218936629607</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2573208471135499</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.636326508564468</v>
+        <v>-4.609855165350894</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8830724956479139</v>
+        <v>0.8936610329333434</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2573208471135499</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.834561077451199</v>
+        <v>-4.808089734237625</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8152758698617606</v>
+        <v>0.8258644071471903</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4555554160002804</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.917562358476478</v>
+        <v>-4.891091015262904</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6204310774523023</v>
+        <v>0.631019614737732</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4741263005274542</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.026176436919809</v>
+        <v>-4.999705093706235</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6971351067941756</v>
+        <v>0.7077236440796051</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4741263005274542</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.112775019900912</v>
+        <v>-5.086303676687338</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6770086997040572</v>
+        <v>0.6875972369894869</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4741263005274542</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.074391357342761</v>
+        <v>-5.047920014129187</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6897816060696864</v>
+        <v>0.7003701433551162</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.435742637969303</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.897275027307595</v>
+        <v>-4.870803684094021</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7573571669290549</v>
+        <v>0.7679457042144844</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.435742637969303</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.942367272141141</v>
+        <v>-4.915895928927567</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7400036607575498</v>
+        <v>0.7505921980429793</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4976386811386928</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.762991850902373</v>
+        <v>-4.736520507688799</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8055408045594712</v>
+        <v>0.8161293418449007</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3408619229679741</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.80800606442298</v>
+        <v>-4.781534721209406</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7683425744828183</v>
+        <v>0.7789311117682478</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3712108182825787</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.075010574695415</v>
+        <v>-5.048539231481841</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.66723233271279</v>
+        <v>0.6778208699982193</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5655738563255273</v>
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.176208356132587</v>
+        <v>-5.118163766246742</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6259571420344221</v>
+        <v>0.6491749779887606</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6377472067711614</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.316407306878697</v>
+        <v>2.314148584738508</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.143732769961815</v>
+        <v>-5.085688180075969</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6365473380570479</v>
+        <v>0.6597651740113863</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6377472067711614</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.314007268433014</v>
+        <v>2.311748546292825</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.124694642254518</v>
+        <v>-5.066650052368672</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6406873083482116</v>
+        <v>0.6639051443025501</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.6959308181023559</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.275621820842542</v>
+        <v>2.273363098702353</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.155821273405136</v>
+        <v>-5.097776683519291</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8058185248266447</v>
+        <v>0.8290363607809832</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.6959308181023559</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.453203689781223</v>
+        <v>2.450944967641033</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.208141654005928</v>
+        <v>-5.150097064120082</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7857237015724619</v>
+        <v>0.8089415375267999</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.6609839580934838</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.475005134772679</v>
+        <v>2.47274641263249</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.228398952534886</v>
+        <v>-5.17035436264904</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7836293125578044</v>
+        <v>0.8068471485121429</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.6609839580934838</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.481013665169605</v>
+        <v>2.478754943029416</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.080655982299883</v>
+        <v>-5.022611392414038</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9218791484438276</v>
+        <v>0.9450969843981656</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.4931766008586006</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.660850727302557</v>
+        <v>2.658592005162368</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.182670664831105</v>
+        <v>-5.124626074945259</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8838668969628198</v>
+        <v>0.9070847329171583</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.4931766008586006</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.663644348834038</v>
+        <v>2.661385626693849</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.17651795877832</v>
+        <v>-5.118473368892475</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8869903277755919</v>
+        <v>0.9102081637299304</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4832593579055013</v>
+        <v>-0.4870238948058163</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.667998320857367</v>
+        <v>2.665739598717178</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.31928329160097</v>
+        <v>-5.261238701715125</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8289646713866423</v>
+        <v>0.8521825073409803</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6297892276284667</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.581419597903887</v>
+        <v>2.579160875763698</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.256985292824848</v>
+        <v>-5.198940702939002</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9202194246939119</v>
+        <v>0.9434372606482504</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6297892276284667</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.647755151700708</v>
+        <v>2.645496429560519</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.05519509515969</v>
+        <v>-4.997150505273845</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7095163761493732</v>
+        <v>0.7327342121037115</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4280064985589973</v>
+        <v>-0.4317710354593123</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.475146939391598</v>
+        <v>2.47288821725141</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.995304413517097</v>
+        <v>-4.937259823631251</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8037628811285857</v>
+        <v>0.826980717082924</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3681158169164038</v>
+        <v>-0.3718803538167188</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.58137158069933</v>
+        <v>2.579112858559141</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.093044958142071</v>
+        <v>-5.035000368256226</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7792943993946397</v>
+        <v>0.8025122353489778</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.384005095049384</v>
+        <v>-0.387769631949699</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.586465749935585</v>
+        <v>2.584207027795396</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.269382718265001</v>
+        <v>-5.211338128379155</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7072952761701394</v>
+        <v>0.7305131121244779</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5603428551723134</v>
+        <v>-0.5641073920726284</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.479199074686499</v>
+        <v>2.47694035254631</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.268693346103777</v>
+        <v>-5.210648756217932</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7060626430745574</v>
+        <v>0.7292804790288958</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5603428551723134</v>
+        <v>-0.5641073920726284</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.477690692726428</v>
+        <v>2.475431970586239</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.27526431115837</v>
+        <v>-5.217219721272524</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7032971244881567</v>
+        <v>0.7265149604424948</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5669138202269064</v>
+        <v>-0.5706783571272214</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.473610981129108</v>
+        <v>2.471352258988919</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.267310340863598</v>
+        <v>-5.209265750977752</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7064787126060654</v>
+        <v>0.7296965485604039</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5669138202269064</v>
+        <v>-0.5706783571272214</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.473610981129108</v>
+        <v>2.471352258988919</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.256936964530511</v>
+        <v>-5.198892374644665</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7170098201671049</v>
+        <v>0.7402276561214429</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5565404438938191</v>
+        <v>-0.560304980794134</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.486216763956765</v>
+        <v>2.483958041816576</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.129252654736215</v>
+        <v>-5.071208064850369</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7729759174595481</v>
+        <v>0.7961937534138865</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4288561340995226</v>
+        <v>-0.4326206709998376</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.567719723208068</v>
+        <v>2.565461001067879</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.189919245138604</v>
+        <v>-5.131874655252759</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7354639537744645</v>
+        <v>0.758681789728803</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5105544508180563</v>
+        <v>-0.5143189877183713</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.50545540565282</v>
+        <v>2.503196683512631</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.124925385204959</v>
+        <v>-5.066880795319113</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7655592003585512</v>
+        <v>0.7887770363128896</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4837238362139009</v>
+        <v>-0.4874883731142159</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.525651477025942</v>
+        <v>2.523392754885753</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.225684020961957</v>
+        <v>-5.167639431076111</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.72941668568683</v>
+        <v>0.7526345216411685</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5725494049409063</v>
+        <v>-0.5763139418412213</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.476517075420817</v>
+        <v>2.474258353280628</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.181481183876056</v>
+        <v>-5.123436593990211</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7529774230490274</v>
+        <v>0.7761952590033658</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5283465678550059</v>
+        <v>-0.5321111047553209</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.508918380200194</v>
+        <v>2.506659658060005</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.218460211539499</v>
+        <v>-5.160415621653653</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7365958124528977</v>
+        <v>0.7598136484072362</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4913726660636754</v>
+        <v>-0.4951372029639903</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.52951272174424</v>
+        <v>2.527253999604051</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.23851829040434</v>
+        <v>-5.180473700518494</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7798203460900015</v>
+        <v>0.8030381820443395</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4913726660636754</v>
+        <v>-0.4951372029639903</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.58076048692728</v>
+        <v>2.578501764787091</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.198587617226449</v>
+        <v>-5.140543027340604</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7942333199554108</v>
+        <v>0.8174511559097488</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.451441992885785</v>
+        <v>-0.4552065297861</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.603159595428267</v>
+        <v>2.600900873288078</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.158117269663745</v>
+        <v>-5.100072679777899</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8053696872187626</v>
+        <v>0.828587523173101</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4109716453230801</v>
+        <v>-0.414736182223395</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.62239003220416</v>
+        <v>2.620131310063971</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.092893088536539</v>
+        <v>-5.034848498650693</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8486467637623498</v>
+        <v>0.8718645997166878</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.3457474641958744</v>
+        <v>-0.3495120010961894</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.678711944973188</v>
+        <v>2.676453222832999</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.143387378893595</v>
+        <v>-5.08534278900775</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8244100199188074</v>
+        <v>0.8476278558731458</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3907682013219487</v>
+        <v>-0.3945327382222636</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.647660474996824</v>
+        <v>2.645401752856635</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.163499034928304</v>
+        <v>-5.105454445042458</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8176221498361644</v>
+        <v>0.8408399857905029</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.3797408563245295</v>
+        <v>-0.3835053932248444</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.655533674326516</v>
+        <v>2.653274952186327</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.751262635249041</v>
+        <v>3.837540381423618</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.26117961420095</v>
+        <v>-5.203135024315104</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9391076891483165</v>
+        <v>0.962325525102655</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4904440516647183</v>
+        <v>-0.4942085885650332</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.749669528143613</v>
+        <v>2.747410806003424</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-681.9%</t>
+          <t>-673.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.0%</t>
+          <t>-276.5%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.4%</t>
+          <t>-261.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-131.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1991"/>
+  <dimension ref="A1:G1992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.118163766246742</v>
+        <v>-5.149737012919013</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6491749779887606</v>
+        <v>0.6365456793198518</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6377472067711614</v>
+        <v>-0.6339826698708464</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.314148584738508</v>
+        <v>2.316407306878697</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.085688180075969</v>
+        <v>-5.117261426748241</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6597651740113863</v>
+        <v>0.6471358753424776</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6377472067711614</v>
+        <v>-0.6339826698708464</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.311748546292825</v>
+        <v>2.314007268433014</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.066650052368672</v>
+        <v>-5.098223299040944</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6639051443025501</v>
+        <v>0.6512758456336414</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6959308181023559</v>
+        <v>-0.6921662812020409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.273363098702353</v>
+        <v>2.275621820842542</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.097776683519291</v>
+        <v>-5.129349930191562</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8290363607809832</v>
+        <v>0.8164070621120745</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6959308181023559</v>
+        <v>-0.6921662812020409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.450944967641033</v>
+        <v>2.453203689781223</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.150097064120082</v>
+        <v>-5.181670310792354</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8089415375267999</v>
+        <v>0.7963122388578912</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6609839580934838</v>
+        <v>-0.6572194211931688</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.47274641263249</v>
+        <v>2.475005134772679</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.17035436264904</v>
+        <v>-5.201927609321312</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8068471485121429</v>
+        <v>0.7942178498432342</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6609839580934838</v>
+        <v>-0.6572194211931688</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.478754943029416</v>
+        <v>2.481013665169605</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.022611392414038</v>
+        <v>-5.054184639086309</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9450969843981656</v>
+        <v>0.9324676857292569</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4931766008586006</v>
+        <v>-0.4894120639582856</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.658592005162368</v>
+        <v>2.660850727302557</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.124626074945259</v>
+        <v>-5.156199321617531</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9070847329171583</v>
+        <v>0.8944554342482496</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4931766008586006</v>
+        <v>-0.4894120639582856</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.661385626693849</v>
+        <v>2.663644348834038</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.118473368892475</v>
+        <v>-5.150046615564746</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9102081637299304</v>
+        <v>0.8975788650610217</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4870238948058163</v>
+        <v>-0.4832593579055013</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.665739598717178</v>
+        <v>2.667998320857367</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.261238701715125</v>
+        <v>-5.292811948387397</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8521825073409803</v>
+        <v>0.8395532086720716</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6297892276284667</v>
+        <v>-0.6260246907281517</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.579160875763698</v>
+        <v>2.581419597903887</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.198940702939002</v>
+        <v>-5.230513949611274</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9434372606482504</v>
+        <v>0.9308079619793417</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6297892276284667</v>
+        <v>-0.6260246907281517</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.645496429560519</v>
+        <v>2.647755151700708</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.997150505273845</v>
+        <v>-5.028723751946116</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7327342121037115</v>
+        <v>0.720104913434803</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4317710354593123</v>
+        <v>-0.4280064985589973</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.47288821725141</v>
+        <v>2.475146939391598</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.937259823631251</v>
+        <v>-4.968833070303523</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.826980717082924</v>
+        <v>0.8143514184140153</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3718803538167188</v>
+        <v>-0.3681158169164038</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.579112858559141</v>
+        <v>2.58137158069933</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.035000368256226</v>
+        <v>-5.066573614928497</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8025122353489778</v>
+        <v>0.789882936680069</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.387769631949699</v>
+        <v>-0.384005095049384</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.584207027795396</v>
+        <v>2.586465749935585</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.211338128379155</v>
+        <v>-5.242911375051427</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7305131121244779</v>
+        <v>0.7178838134555692</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5641073920726284</v>
+        <v>-0.5603428551723134</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.47694035254631</v>
+        <v>2.479199074686499</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.210648756217932</v>
+        <v>-5.242222002890204</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7292804790288958</v>
+        <v>0.7166511803599871</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5641073920726284</v>
+        <v>-0.5603428551723134</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.475431970586239</v>
+        <v>2.477690692726428</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.217219721272524</v>
+        <v>-5.248792967944796</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7265149604424948</v>
+        <v>0.713885661773586</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5706783571272214</v>
+        <v>-0.5669138202269064</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.471352258988919</v>
+        <v>2.473610981129108</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.209265750977752</v>
+        <v>-5.240838997650024</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7296965485604039</v>
+        <v>0.7170672498914952</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5706783571272214</v>
+        <v>-0.5669138202269064</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.471352258988919</v>
+        <v>2.473610981129108</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.198892374644665</v>
+        <v>-5.230465621316937</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7402276561214429</v>
+        <v>0.7275983574525342</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.560304980794134</v>
+        <v>-0.5565404438938191</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.483958041816576</v>
+        <v>2.486216763956765</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.071208064850369</v>
+        <v>-5.102781311522641</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7961937534138865</v>
+        <v>0.7835644547449778</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4326206709998376</v>
+        <v>-0.4288561340995226</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.565461001067879</v>
+        <v>2.567719723208068</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.131874655252759</v>
+        <v>-5.16344790192503</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.758681789728803</v>
+        <v>0.7460524910598942</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5143189877183713</v>
+        <v>-0.5105544508180563</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.503196683512631</v>
+        <v>2.50545540565282</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.066880795319113</v>
+        <v>-5.098454041991385</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7887770363128896</v>
+        <v>0.7761477376439809</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4874883731142159</v>
+        <v>-0.4837238362139009</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.523392754885753</v>
+        <v>2.525651477025942</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.167639431076111</v>
+        <v>-5.199212677748383</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7526345216411685</v>
+        <v>0.7400052229722598</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5763139418412213</v>
+        <v>-0.5725494049409063</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.474258353280628</v>
+        <v>2.476517075420817</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.123436593990211</v>
+        <v>-5.155009840662482</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7761952590033658</v>
+        <v>0.7635659603344571</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5321111047553209</v>
+        <v>-0.5283465678550059</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.506659658060005</v>
+        <v>2.508918380200194</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.160415621653653</v>
+        <v>-5.191988868325925</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7598136484072362</v>
+        <v>0.7471843497383275</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4951372029639903</v>
+        <v>-0.4913726660636754</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.527253999604051</v>
+        <v>2.52951272174424</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.180473700518494</v>
+        <v>-5.212046947190766</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8030381820443395</v>
+        <v>0.7904088833754308</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4951372029639903</v>
+        <v>-0.4913726660636754</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.578501764787091</v>
+        <v>2.58076048692728</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.140543027340604</v>
+        <v>-5.172116274012875</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8174511559097488</v>
+        <v>0.8048218572408401</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.4552065297861</v>
+        <v>-0.451441992885785</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.600900873288078</v>
+        <v>2.603159595428267</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.100072679777899</v>
+        <v>-5.131645926450171</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.828587523173101</v>
+        <v>0.8159582245041923</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.414736182223395</v>
+        <v>-0.4109716453230801</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.620131310063971</v>
+        <v>2.62239003220416</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.034848498650693</v>
+        <v>-5.066421745322965</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8718645997166878</v>
+        <v>0.8592353010477791</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.3495120010961894</v>
+        <v>-0.3457474641958744</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.676453222832999</v>
+        <v>2.678711944973188</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.08534278900775</v>
+        <v>-5.116916035680021</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8476278558731458</v>
+        <v>0.8349985572042371</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3945327382222636</v>
+        <v>-0.3907682013219487</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.645401752856635</v>
+        <v>2.647660474996824</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.105454445042458</v>
+        <v>-5.13702769171473</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8408399857905029</v>
+        <v>0.8282106871215942</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.3835053932248444</v>
+        <v>-0.3797408563245295</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.653274952186327</v>
+        <v>2.655533674326516</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,45 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.837540381423618</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.203135024315104</v>
+        <v>-5.116939513884771</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.962325525102655</v>
+        <v>0.9968037292747884</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4942085885650332</v>
+        <v>-0.3697805899768837</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.747410806003424</v>
+        <v>2.822067605156314</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="2" t="n">
+        <v>45454</v>
+      </c>
+      <c r="B1992" t="n">
+        <v>3.838651918982235</v>
+      </c>
+      <c r="C1992" t="n">
+        <v>3.150745321695505</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>-5.116939513884771</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>0.9968037292747884</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>-0.3697805899768837</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>3.143809118681873</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.3%</t>
+          <t>-680.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.5%</t>
+          <t>-279.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-157.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.0%</t>
+          <t>-271.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-138.4%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.230150153767569</v>
+        <v>-5.254046318963272</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8870453847056705</v>
+        <v>0.8774869186273895</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6204392541527666</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.0706350502482</v>
+        <v>-5.094531215443903</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9519972705537203</v>
+        <v>0.9424388044754393</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4609241506333966</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.925962905148462</v>
+        <v>-4.949859070344165</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.019954231155055</v>
+        <v>1.010395765076774</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3162520055336592</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.985837732506154</v>
+        <v>-5.009733897701858</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9820417916134043</v>
+        <v>0.9724833255351228</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3761268328913513</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.899038234727145</v>
+        <v>-4.922934399922848</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.039162084047574</v>
+        <v>1.029603617969293</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3761268328913513</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.901507941188951</v>
+        <v>-4.925404106384654</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.038246602836264</v>
+        <v>1.028688136757983</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3785965393531575</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.969878127512962</v>
+        <v>-4.993774292708665</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.021905450781362</v>
+        <v>1.01234698470308</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3693208403169426</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.078416308429095</v>
+        <v>-5.102312473624798</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9689268870467993</v>
+        <v>0.9593684209685183</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3693208403169426</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.109409467757801</v>
+        <v>-5.133305632953504</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7812391883557042</v>
+        <v>0.7716807222774227</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3693208403169426</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.933935207965332</v>
+        <v>-4.957831373161035</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8559961242644794</v>
+        <v>0.8464376581861981</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3693208403169426</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.044871460606581</v>
+        <v>-5.068767625802284</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7873636519691867</v>
+        <v>0.7778051858909056</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3693208403169426</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.053153534751639</v>
+        <v>-5.077049699947342</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7871822075310688</v>
+        <v>0.7776237414527878</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3776029144620009</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.895227935816346</v>
+        <v>-4.919124101012049</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8605248335373186</v>
+        <v>0.8509663674590373</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3776029144620009</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.808984472789969</v>
+        <v>-4.832880637985672</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8899684893217299</v>
+        <v>0.8804100232434489</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3776029144620009</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.854291292188949</v>
+        <v>-4.878187457384652</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8636215370066636</v>
+        <v>0.8540630709283823</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4184130774712317</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.88332439689125</v>
+        <v>-4.907220562086953</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8525601681588446</v>
+        <v>0.8430017020805636</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4184130774712317</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.79051391544039</v>
+        <v>-4.814410080636093</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8189570526305543</v>
+        <v>0.809398586552273</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3256025960203724</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.834903384769818</v>
+        <v>-4.858799549965521</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.803074740823384</v>
+        <v>0.7935162747451028</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3699920653498001</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.722232166533567</v>
+        <v>-4.74612833172927</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.843218936629607</v>
+        <v>0.833660470551326</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2573208471135499</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.609855165350894</v>
+        <v>-4.633751330546597</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8936610329333434</v>
+        <v>0.8841025668550624</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2573208471135499</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.808089734237625</v>
+        <v>-4.831985899433328</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8258644071471903</v>
+        <v>0.8163059410689091</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4555554160002804</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.891091015262904</v>
+        <v>-4.914987180458607</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.631019614737732</v>
+        <v>0.6214611486594508</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4741263005274542</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.999705093706235</v>
+        <v>-5.023601258901938</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7077236440796051</v>
+        <v>0.6981651780013238</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4741263005274542</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.086303676687338</v>
+        <v>-5.110199841883041</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6875972369894869</v>
+        <v>0.6780387709112059</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4741263005274542</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.047920014129187</v>
+        <v>-5.07181617932489</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7003701433551162</v>
+        <v>0.6908116772768347</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.435742637969303</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.870803684094021</v>
+        <v>-4.894699849289724</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7679457042144844</v>
+        <v>0.7583872381362031</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.435742637969303</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.915895928927567</v>
+        <v>-4.93979209412327</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7505921980429793</v>
+        <v>0.741033731964698</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4976386811386928</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.736520507688799</v>
+        <v>-4.760416672884502</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8161293418449007</v>
+        <v>0.8065708757666195</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3408619229679741</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.781534721209406</v>
+        <v>-4.805430886405109</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7789311117682478</v>
+        <v>0.7693726456899666</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3712108182825787</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.048539231481841</v>
+        <v>-5.072435396677544</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6778208699982193</v>
+        <v>0.6682624039199383</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5655738563255273</v>
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.149737012919013</v>
+        <v>-5.10371085872983</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6365456793198518</v>
+        <v>0.6549561409955253</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6183043431968211</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.316407306878697</v>
+        <v>2.325814302883112</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.117261426748241</v>
+        <v>-5.071235272559058</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6471358753424776</v>
+        <v>0.6655463370181507</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6183043431968211</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.314007268433014</v>
+        <v>2.323414264437429</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.098223299040944</v>
+        <v>-5.05219714485176</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6512758456336414</v>
+        <v>0.6696863073093149</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.6764879545280157</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.275621820842542</v>
+        <v>2.285028816846957</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.129349930191562</v>
+        <v>-5.083323776002379</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8164070621120745</v>
+        <v>0.834817523787748</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.6764879545280157</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.453203689781223</v>
+        <v>2.462610685785638</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.181670310792354</v>
+        <v>-5.135644156603171</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7963122388578912</v>
+        <v>0.8147227005335647</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.6415410945191435</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.475005134772679</v>
+        <v>2.484412130777094</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.201927609321312</v>
+        <v>-5.155901455132128</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7942178498432342</v>
+        <v>0.8126283115189077</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.6415410945191435</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.481013665169605</v>
+        <v>2.49042066117402</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.054184639086309</v>
+        <v>-5.008158484897126</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9324676857292569</v>
+        <v>0.9508781474049304</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.4737337372842604</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.660850727302557</v>
+        <v>2.670257723306972</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.156199321617531</v>
+        <v>-5.110173167428347</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8944554342482496</v>
+        <v>0.9128658959239231</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.4737337372842604</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.663644348834038</v>
+        <v>2.673051344838453</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.150046615564746</v>
+        <v>-5.104020461375563</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8975788650610217</v>
+        <v>0.9159893267366952</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4832593579055013</v>
+        <v>-0.4675810312314761</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.667998320857367</v>
+        <v>2.677405316861782</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.292811948387397</v>
+        <v>-5.246785794198213</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8395532086720716</v>
+        <v>0.8579636703477451</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6103463640541265</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.581419597903887</v>
+        <v>2.590826593908302</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.230513949611274</v>
+        <v>-5.184487795422091</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9308079619793417</v>
+        <v>0.9492184236550152</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6103463640541265</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.647755151700708</v>
+        <v>2.657162147705123</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.028723751946116</v>
+        <v>-4.982697597756933</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.720104913434803</v>
+        <v>0.7385153751104763</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4280064985589973</v>
+        <v>-0.4123281718849721</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.475146939391598</v>
+        <v>2.484553935396014</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.968833070303523</v>
+        <v>-4.92280691611434</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8143514184140153</v>
+        <v>0.8327618800896888</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3681158169164038</v>
+        <v>-0.3524374902423786</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.58137158069933</v>
+        <v>2.590778576703745</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.066573614928497</v>
+        <v>-5.020547460739314</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.789882936680069</v>
+        <v>0.8082933983557425</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.384005095049384</v>
+        <v>-0.3683267683753588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.586465749935585</v>
+        <v>2.59587274594</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.242911375051427</v>
+        <v>-5.196885220862243</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7178838134555692</v>
+        <v>0.7362942751312427</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5603428551723134</v>
+        <v>-0.5446645284982882</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.479199074686499</v>
+        <v>2.488606070690914</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.242222002890204</v>
+        <v>-5.19619584870102</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7166511803599871</v>
+        <v>0.7350616420356606</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5603428551723134</v>
+        <v>-0.5446645284982882</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.477690692726428</v>
+        <v>2.487097688730843</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.248792967944796</v>
+        <v>-5.202766813755613</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.713885661773586</v>
+        <v>0.7322961234492595</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5669138202269064</v>
+        <v>-0.5512354935528812</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.473610981129108</v>
+        <v>2.483017977133524</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.240838997650024</v>
+        <v>-5.19481284346084</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7170672498914952</v>
+        <v>0.7354777115671682</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5669138202269064</v>
+        <v>-0.5512354935528812</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.473610981129108</v>
+        <v>2.483017977133524</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.230465621316937</v>
+        <v>-5.184439467127754</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7275983574525342</v>
+        <v>0.7460088191282077</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5565404438938191</v>
+        <v>-0.5408621172197938</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.486216763956765</v>
+        <v>2.49562375996118</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.102781311522641</v>
+        <v>-5.056755157333457</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7835644547449778</v>
+        <v>0.8019749164206513</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4288561340995226</v>
+        <v>-0.4131778074254974</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.567719723208068</v>
+        <v>2.577126719212483</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.16344790192503</v>
+        <v>-5.117421747735847</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7460524910598942</v>
+        <v>0.7644629527355677</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5105544508180563</v>
+        <v>-0.494876124144031</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.50545540565282</v>
+        <v>2.514862401657235</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.098454041991385</v>
+        <v>-5.052427887802201</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7761477376439809</v>
+        <v>0.7945581993196544</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4837238362139009</v>
+        <v>-0.4680455095398757</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.525651477025942</v>
+        <v>2.535058473030357</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.199212677748383</v>
+        <v>-5.153186523559199</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7400052229722598</v>
+        <v>0.7584156846479333</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5725494049409063</v>
+        <v>-0.5568710782668811</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.476517075420817</v>
+        <v>2.485924071425232</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.155009840662482</v>
+        <v>-5.108983686473299</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7635659603344571</v>
+        <v>0.7819764220101306</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5283465678550059</v>
+        <v>-0.5126682411809806</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.508918380200194</v>
+        <v>2.518325376204609</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.191988868325925</v>
+        <v>-5.145962714136742</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7471843497383275</v>
+        <v>0.765594811414001</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4913726660636754</v>
+        <v>-0.4756943393896501</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.52951272174424</v>
+        <v>2.538919717748655</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.212046947190766</v>
+        <v>-5.166020793001582</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7904088833754308</v>
+        <v>0.8088193450511043</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4913726660636754</v>
+        <v>-0.4756943393896501</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.58076048692728</v>
+        <v>2.590167482931695</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.172116274012875</v>
+        <v>-5.126090119823692</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8048218572408401</v>
+        <v>0.8232323189165136</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.451441992885785</v>
+        <v>-0.4357636662117598</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.603159595428267</v>
+        <v>2.612566591432682</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.131645926450171</v>
+        <v>-5.085619772260987</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8159582245041923</v>
+        <v>0.8343686861798654</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.4109716453230801</v>
+        <v>-0.3952933186490548</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.62239003220416</v>
+        <v>2.631797028208575</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.066421745322965</v>
+        <v>-5.020395591133782</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8592353010477791</v>
+        <v>0.8776457627234526</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.3457474641958744</v>
+        <v>-0.3300691375218492</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.678711944973188</v>
+        <v>2.688118940977603</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.116916035680021</v>
+        <v>-5.070889881490838</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8349985572042371</v>
+        <v>0.8534090188799106</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3907682013219487</v>
+        <v>-0.3750898746479234</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.647660474996824</v>
+        <v>2.657067471001239</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.13702769171473</v>
+        <v>-5.091001537525546</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8282106871215942</v>
+        <v>0.8466211487972677</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.3797408563245295</v>
+        <v>-0.3640625296505042</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.655533674326516</v>
+        <v>2.664940670330931</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.116939513884771</v>
+        <v>-5.1914666852655</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9968037292747884</v>
+        <v>0.9669928607224967</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3697805899768837</v>
+        <v>-0.4768133793889304</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.822067605156314</v>
+        <v>2.757847931509086</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.838651918982235</v>
+        <v>3.837688931134604</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.150745321695505</v>
+        <v>3.083224171675081</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.116939513884771</v>
+        <v>-5.1914666852655</v>
       </c>
       <c r="E1992" t="n">
-        <v>0.9968037292747884</v>
+        <v>0.9669928607224967</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3697805899768837</v>
+        <v>-0.4768133793889304</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.143809118681873</v>
+        <v>3.076287968661449</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.7%</t>
+          <t>-664.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.5%</t>
+          <t>-273.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-156.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.7%</t>
+          <t>-252.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.4%</t>
+          <t>-119.7%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.254046318963272</v>
+        <v>-5.230150153767569</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8774869186273895</v>
+        <v>0.8870453847056705</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6204392541527666</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.094531215443903</v>
+        <v>-5.0706350502482</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9424388044754393</v>
+        <v>0.9519972705537203</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4609241506333966</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.949859070344165</v>
+        <v>-4.925962905148462</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.010395765076774</v>
+        <v>1.019954231155055</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3162520055336592</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.009733897701858</v>
+        <v>-4.985837732506154</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9724833255351228</v>
+        <v>0.9820417916134043</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3761268328913513</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.922934399922848</v>
+        <v>-4.899038234727145</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.029603617969293</v>
+        <v>1.039162084047574</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3761268328913513</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.925404106384654</v>
+        <v>-4.901507941188951</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.028688136757983</v>
+        <v>1.038246602836264</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3785965393531575</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.993774292708665</v>
+        <v>-4.969878127512962</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.01234698470308</v>
+        <v>1.021905450781362</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3693208403169426</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.102312473624798</v>
+        <v>-5.078416308429095</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9593684209685183</v>
+        <v>0.9689268870467993</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3693208403169426</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.133305632953504</v>
+        <v>-5.109409467757801</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7716807222774227</v>
+        <v>0.7812391883557042</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3693208403169426</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.957831373161035</v>
+        <v>-4.933935207965332</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8464376581861981</v>
+        <v>0.8559961242644794</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3693208403169426</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.068767625802284</v>
+        <v>-5.044871460606581</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7778051858909056</v>
+        <v>0.7873636519691867</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3693208403169426</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.077049699947342</v>
+        <v>-5.053153534751639</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7776237414527878</v>
+        <v>0.7871822075310688</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3776029144620009</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.919124101012049</v>
+        <v>-4.895227935816346</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8509663674590373</v>
+        <v>0.8605248335373186</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3776029144620009</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.832880637985672</v>
+        <v>-4.808984472789969</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8804100232434489</v>
+        <v>0.8899684893217299</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3776029144620009</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.878187457384652</v>
+        <v>-4.854291292188949</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8540630709283823</v>
+        <v>0.8636215370066636</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4184130774712317</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.907220562086953</v>
+        <v>-4.88332439689125</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8430017020805636</v>
+        <v>0.8525601681588446</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4184130774712317</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.814410080636093</v>
+        <v>-4.79051391544039</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.809398586552273</v>
+        <v>0.8189570526305543</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3256025960203724</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.858799549965521</v>
+        <v>-4.834903384769818</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7935162747451028</v>
+        <v>0.803074740823384</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3699920653498001</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.74612833172927</v>
+        <v>-4.722232166533567</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.833660470551326</v>
+        <v>0.843218936629607</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2573208471135499</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.633751330546597</v>
+        <v>-4.609855165350894</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8841025668550624</v>
+        <v>0.8936610329333434</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2573208471135499</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.831985899433328</v>
+        <v>-4.808089734237625</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8163059410689091</v>
+        <v>0.8258644071471903</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4555554160002804</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.914987180458607</v>
+        <v>-4.891091015262904</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6214611486594508</v>
+        <v>0.631019614737732</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4741263005274542</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.023601258901938</v>
+        <v>-4.999705093706235</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6981651780013238</v>
+        <v>0.7077236440796051</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4741263005274542</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.110199841883041</v>
+        <v>-5.086303676687338</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6780387709112059</v>
+        <v>0.6875972369894869</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4741263005274542</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.07181617932489</v>
+        <v>-5.047920014129187</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6908116772768347</v>
+        <v>0.7003701433551162</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.435742637969303</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.894699849289724</v>
+        <v>-4.870803684094021</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7583872381362031</v>
+        <v>0.7679457042144844</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.435742637969303</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.93979209412327</v>
+        <v>-4.915895928927567</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.741033731964698</v>
+        <v>0.7505921980429793</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4976386811386928</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.760416672884502</v>
+        <v>-4.736520507688799</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8065708757666195</v>
+        <v>0.8161293418449007</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3408619229679741</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.805430886405109</v>
+        <v>-4.781534721209406</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7693726456899666</v>
+        <v>0.7789311117682478</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3712108182825787</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.072435396677544</v>
+        <v>-5.048539231481841</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6682624039199383</v>
+        <v>0.6778208699982193</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5655738563255273</v>
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.10371085872983</v>
+        <v>-5.149737012919013</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6549561409955253</v>
+        <v>0.6365456793198518</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6183043431968211</v>
+        <v>-0.6339826698708464</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.325814302883112</v>
+        <v>2.316407306878697</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.071235272559058</v>
+        <v>-5.117261426748241</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6655463370181507</v>
+        <v>0.6471358753424776</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6183043431968211</v>
+        <v>-0.6339826698708464</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.323414264437429</v>
+        <v>2.314007268433014</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.05219714485176</v>
+        <v>-5.098223299040944</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6696863073093149</v>
+        <v>0.6512758456336414</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6764879545280157</v>
+        <v>-0.6921662812020409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.285028816846957</v>
+        <v>2.275621820842542</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.083323776002379</v>
+        <v>-5.129349930191562</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.834817523787748</v>
+        <v>0.8164070621120745</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6764879545280157</v>
+        <v>-0.6921662812020409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.462610685785638</v>
+        <v>2.453203689781223</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.135644156603171</v>
+        <v>-5.181670310792354</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8147227005335647</v>
+        <v>0.7963122388578912</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6415410945191435</v>
+        <v>-0.6572194211931688</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.484412130777094</v>
+        <v>2.475005134772679</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.155901455132128</v>
+        <v>-5.201927609321312</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8126283115189077</v>
+        <v>0.7942178498432342</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6415410945191435</v>
+        <v>-0.6572194211931688</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.49042066117402</v>
+        <v>2.481013665169605</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.008158484897126</v>
+        <v>-5.054184639086309</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9508781474049304</v>
+        <v>0.9324676857292569</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4737337372842604</v>
+        <v>-0.4894120639582856</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.670257723306972</v>
+        <v>2.660850727302557</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.110173167428347</v>
+        <v>-5.156199321617531</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9128658959239231</v>
+        <v>0.8944554342482496</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4737337372842604</v>
+        <v>-0.4894120639582856</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.673051344838453</v>
+        <v>2.663644348834038</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.104020461375563</v>
+        <v>-5.150046615564746</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9159893267366952</v>
+        <v>0.8975788650610217</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4675810312314761</v>
+        <v>-0.4832593579055013</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.677405316861782</v>
+        <v>2.667998320857367</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.246785794198213</v>
+        <v>-5.292811948387397</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8579636703477451</v>
+        <v>0.8395532086720716</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6103463640541265</v>
+        <v>-0.6260246907281517</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.590826593908302</v>
+        <v>2.581419597903887</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.184487795422091</v>
+        <v>-5.230513949611274</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9492184236550152</v>
+        <v>0.9308079619793417</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6103463640541265</v>
+        <v>-0.6260246907281517</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.657162147705123</v>
+        <v>2.647755151700708</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.982697597756933</v>
+        <v>-5.028723751946116</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7385153751104763</v>
+        <v>0.720104913434803</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4123281718849721</v>
+        <v>-0.4280064985589973</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.484553935396014</v>
+        <v>2.475146939391598</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.92280691611434</v>
+        <v>-4.968833070303523</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8327618800896888</v>
+        <v>0.8143514184140153</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3524374902423786</v>
+        <v>-0.3681158169164038</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.590778576703745</v>
+        <v>2.58137158069933</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.020547460739314</v>
+        <v>-5.066573614928497</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8082933983557425</v>
+        <v>0.789882936680069</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3683267683753588</v>
+        <v>-0.384005095049384</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.59587274594</v>
+        <v>2.586465749935585</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.196885220862243</v>
+        <v>-5.037449223661643</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7362942751312427</v>
+        <v>0.8000686740114826</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5446645284982882</v>
+        <v>-0.3548807037825291</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.488606070690914</v>
+        <v>2.60247636552037</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.19619584870102</v>
+        <v>-5.036759851500419</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7350616420356606</v>
+        <v>0.7988360409159005</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5446645284982882</v>
+        <v>-0.3548807037825291</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.487097688730843</v>
+        <v>2.600967983560298</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.202766813755613</v>
+        <v>-5.043330816555012</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7322961234492595</v>
+        <v>0.7960705223294999</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5512354935528812</v>
+        <v>-0.361451668837122</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.483017977133524</v>
+        <v>2.596888271962979</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.19481284346084</v>
+        <v>-5.03537684626024</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7354777115671682</v>
+        <v>0.7992521104474086</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5512354935528812</v>
+        <v>-0.361451668837122</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.483017977133524</v>
+        <v>2.596888271962979</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.184439467127754</v>
+        <v>-5.025003469927153</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7460088191282077</v>
+        <v>0.8097832180084481</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5408621172197938</v>
+        <v>-0.3510782925040347</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.49562375996118</v>
+        <v>2.609494054790636</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.056755157333457</v>
+        <v>-4.897319160132857</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8019749164206513</v>
+        <v>0.8657493153008913</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4131778074254974</v>
+        <v>-0.2233939827097383</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.577126719212483</v>
+        <v>2.690997014041939</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.117421747735847</v>
+        <v>-4.957985750535245</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7644629527355677</v>
+        <v>0.8282373516158081</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.494876124144031</v>
+        <v>-0.3050922994282719</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.514862401657235</v>
+        <v>2.628732696486691</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.052427887802201</v>
+        <v>-4.8929918906016</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7945581993196544</v>
+        <v>0.8583325981998948</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4680455095398757</v>
+        <v>-0.2782616848241166</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.535058473030357</v>
+        <v>2.648928767859812</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.153186523559199</v>
+        <v>-4.993750526358598</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7584156846479333</v>
+        <v>0.8221900835281737</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5568710782668811</v>
+        <v>-0.367087253551122</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.485924071425232</v>
+        <v>2.599794366254687</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.108983686473299</v>
+        <v>-4.949547689272698</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7819764220101306</v>
+        <v>0.845750820890371</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5126682411809806</v>
+        <v>-0.3228844164652215</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.518325376204609</v>
+        <v>2.632195671034065</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.145962714136742</v>
+        <v>-4.98652671693614</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.765594811414001</v>
+        <v>0.8293692102942414</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4756943393896501</v>
+        <v>-0.285910514673891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.538919717748655</v>
+        <v>2.652790012578111</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.166020793001582</v>
+        <v>-5.006584795800981</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8088193450511043</v>
+        <v>0.8725937439313449</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4756943393896501</v>
+        <v>-0.285910514673891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.590167482931695</v>
+        <v>2.70403777776115</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.126090119823692</v>
+        <v>-4.96665412262309</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8232323189165136</v>
+        <v>0.8870067177967542</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.4357636662117598</v>
+        <v>-0.2459798414960007</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.612566591432682</v>
+        <v>2.726436886262138</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.085619772260987</v>
+        <v>-4.926183775060386</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8343686861798654</v>
+        <v>0.8981430850601062</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.3952933186490548</v>
+        <v>-0.2055094939332957</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.631797028208575</v>
+        <v>2.745667323038031</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.020395591133782</v>
+        <v>-4.86095959393318</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8776457627234526</v>
+        <v>0.9414201616036932</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.3300691375218492</v>
+        <v>-0.1402853128060901</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.688118940977603</v>
+        <v>2.801989235807059</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.070889881490838</v>
+        <v>-4.911453884290236</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8534090188799106</v>
+        <v>0.917183417760151</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3750898746479234</v>
+        <v>-0.1853060499321643</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.657067471001239</v>
+        <v>2.770937765830694</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.091001537525546</v>
+        <v>-4.931565540324945</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8466211487972677</v>
+        <v>0.9103955476775081</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.3640625296505042</v>
+        <v>-0.1742787049347451</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.664940670330931</v>
+        <v>2.778810965160386</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.1914666852655</v>
+        <v>-5.029246119597591</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9669928607224967</v>
+        <v>1.03188108698966</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.4768133793889304</v>
+        <v>-0.2849819002749339</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.757847931509086</v>
+        <v>2.872946818977484</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.837688931134604</v>
+        <v>3.896001767077581</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.083224171675081</v>
+        <v>3.270237721474783</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.1914666852655</v>
+        <v>-5.029246119597591</v>
       </c>
       <c r="E1992" t="n">
-        <v>0.9669928607224967</v>
+        <v>1.03188108698966</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.4768133793889304</v>
+        <v>-0.2849819002749339</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.076287968661449</v>
+        <v>3.263301518461151</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>450.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.5%</t>
+          <t>-666.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.0%</t>
+          <t>-251.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.3%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-252.5%</t>
+          <t>-254.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-119.7%</t>
+          <t>-137.1%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.633373957223309</v>
+        <v>-8.680778725972655</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2949547830412071</v>
+        <v>-0.3139166905409452</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.017272168218961</v>
+        <v>-2.064676936968306</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.948387923230488</v>
+        <v>1.919945061980881</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.483707566215795</v>
+        <v>-8.53111233496514</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2379804369511609</v>
+        <v>-0.2569423444508989</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.924368676976425</v>
+        <v>-1.97177344572577</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.00123780766305</v>
+        <v>1.972794946413443</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.351432092584908</v>
+        <v>-8.398836861334253</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1897027607517789</v>
+        <v>-0.208664668251517</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.792093203345538</v>
+        <v>-1.839497972094883</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.075970578588609</v>
+        <v>2.047527717339002</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.160832417911754</v>
+        <v>-8.208237186661099</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1106478301948806</v>
+        <v>-0.1296097376946186</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.64889829742173</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.193145444080137</v>
+        <v>2.164702582830531</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.911832619228173</v>
+        <v>-7.959237387977518</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.001858430502210684</v>
+        <v>-0.01710347699752779</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.601493528672385</v>
+        <v>-1.64889829742173</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.206051785303796</v>
+        <v>2.177608924054189</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.017422609001278</v>
+        <v>-8.064827377750623</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.16835349500625</v>
+        <v>-0.187315402505988</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.70708351844549</v>
+        <v>-1.754488287194834</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.014721861840715</v>
+        <v>1.986279000591108</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.036157511119875</v>
+        <v>-8.08356227986922</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1273031139766023</v>
+        <v>-0.1462650214763404</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.712679528105621</v>
+        <v>-1.760084296854966</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059908597921723</v>
+        <v>2.031465736672116</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.888217469712275</v>
+        <v>-7.935622238461621</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1880060201017302</v>
+        <v>-0.2069679276014682</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.692358612197063</v>
+        <v>-1.739763380946408</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.95222222477869</v>
+        <v>1.923779363529083</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.871059319580981</v>
+        <v>-7.918464088330326</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1898567463026906</v>
+        <v>-0.208818653802429</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.722605230815114</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.953803128603988</v>
+        <v>1.925360267354381</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.827510912810291</v>
+        <v>-7.874915681559636</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1793979956895075</v>
+        <v>-0.198359903189246</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.722605230815114</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.946842516508895</v>
+        <v>1.918399655259288</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.585362519356432</v>
+        <v>-7.632767288105778</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06807628392682119</v>
+        <v>-0.08703819142655966</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.722605230815114</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.961304870890038</v>
+        <v>1.932862009640431</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.477103382233911</v>
+        <v>-7.524508150983256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03024050861861749</v>
+        <v>-0.04920241611835596</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.675200462065769</v>
+        <v>-1.722605230815114</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.955836991349233</v>
+        <v>1.927394130099626</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.35381224741678</v>
+        <v>-7.401217016166125</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01657403931881163</v>
+        <v>-0.0023878681809264</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.551909327248639</v>
+        <v>-1.599314095997983</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.027309766250088</v>
+        <v>1.998866905000481</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.332663048513337</v>
+        <v>-7.380067817262682</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03273469711751398</v>
+        <v>0.01377278961777595</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.57816489709454</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.047700263829479</v>
+        <v>2.019257402579872</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.088897606529892</v>
+        <v>-7.136302375279238</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1260215822579425</v>
+        <v>0.1070596747582044</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.530760128345195</v>
+        <v>-1.57816489709454</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.04348097217653</v>
+        <v>2.015038110926923</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.987134786252597</v>
+        <v>-7.034539555001943</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1688510242888763</v>
+        <v>0.1498891167891383</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.564945828702111</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.053536727132003</v>
+        <v>2.025093865882396</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.737284392303523</v>
+        <v>-6.784689161052868</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2615332568522084</v>
+        <v>0.2425713493524704</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.564945828702111</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.046278802115705</v>
+        <v>2.017835940866099</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.56139229983609</v>
+        <v>-6.608797068585435</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3354892173598305</v>
+        <v>0.316527309860092</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.517541059952767</v>
+        <v>-1.564945828702111</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.049877925636354</v>
+        <v>2.021435064386747</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.389945836813626</v>
+        <v>-6.437350605562972</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4173953086233695</v>
+        <v>0.3984334011236315</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.346094596930303</v>
+        <v>-1.393499365679648</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.166073309504386</v>
+        <v>2.137630448254779</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.164912837144803</v>
+        <v>-6.212317605894149</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5064289861071956</v>
+        <v>0.4874670786074575</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.12106159726148</v>
+        <v>-1.168466366010825</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.300113586921976</v>
+        <v>2.27167072567237</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.101277094910869</v>
+        <v>-6.148681863660214</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5365780840550864</v>
+        <v>0.5176161765553484</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.057425855027546</v>
+        <v>-1.104830623776891</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.342989833316654</v>
+        <v>2.314546972067047</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.057514913605027</v>
+        <v>-6.104919682354373</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5352772153612189</v>
+        <v>0.5163153078614808</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.057425855027546</v>
+        <v>-1.104830623776891</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.32418409210045</v>
+        <v>2.295741230850843</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.817084416800167</v>
+        <v>-5.864489185549512</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6331924907080406</v>
+        <v>0.6142305832083021</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.8644001269720305</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.470185466808243</v>
+        <v>2.441742605558637</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.744841848628973</v>
+        <v>-5.792246617378318</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6660188318113387</v>
+        <v>0.6470569243116002</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8169953582226857</v>
+        <v>-0.8644001269720305</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.474114780643064</v>
+        <v>2.445671919393457</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.691843526347585</v>
+        <v>-5.73924829509693</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6878967446412338</v>
+        <v>0.6689348371414954</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.8090638679700917</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.507995119961567</v>
+        <v>2.47955225871196</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.583038640867858</v>
+        <v>-5.630443409617203</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7284167700531179</v>
+        <v>0.7094548625533799</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7616590992207468</v>
+        <v>-0.8090638679700917</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.504993191181561</v>
+        <v>2.476550329931953</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.363017842830847</v>
+        <v>-5.410422611580192</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8180041262785362</v>
+        <v>0.7990422187787982</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.6678440229021114</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.591304135232963</v>
+        <v>2.562861273983356</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.230150153767569</v>
+        <v>-5.277554922516915</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8870453847056705</v>
+        <v>0.8680834772059325</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6204392541527666</v>
+        <v>-0.6678440229021114</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.607198318034786</v>
+        <v>2.578755456785179</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.0706350502482</v>
+        <v>-5.118039818997545</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9519972705537203</v>
+        <v>0.9330353630539823</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4609241506333966</v>
+        <v>-0.5083289193827415</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.70405322458671</v>
+        <v>2.675610363337103</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.925962905148462</v>
+        <v>-4.973367673897807</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.019954231155055</v>
+        <v>1.000992323655317</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3162520055336592</v>
+        <v>-0.3636567742830041</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.800944614207992</v>
+        <v>2.772501752958386</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.985837732506154</v>
+        <v>-5.0332425012555</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9820417916134043</v>
+        <v>0.9630798841136663</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3761268328913513</v>
+        <v>-0.4235316016406962</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.751057209194803</v>
+        <v>2.722614347945196</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.899038234727145</v>
+        <v>-4.946443003476491</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.039162084047574</v>
+        <v>1.020200176547836</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3761268328913513</v>
+        <v>-0.4235316016406962</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.773457702517369</v>
+        <v>2.745014841267762</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.901507941188951</v>
+        <v>-4.948912709938297</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.038246602836264</v>
+        <v>1.019284695336526</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3785965393531575</v>
+        <v>-0.4260013081025024</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.772048280013697</v>
+        <v>2.743605418764091</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.969878127512962</v>
+        <v>-5.017282896262307</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.021905450781362</v>
+        <v>1.002943543281623</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3693208403169426</v>
+        <v>-0.4167256090662874</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.788620621910128</v>
+        <v>2.760177760660521</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.078416308429095</v>
+        <v>-5.125821077178441</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9689268870467993</v>
+        <v>0.9499649795470613</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3693208403169426</v>
+        <v>-0.4167256090662874</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.779057330542019</v>
+        <v>2.750614469292413</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.109409467757801</v>
+        <v>-5.156814236507146</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7812391883557042</v>
+        <v>0.7622772808559661</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3693208403169426</v>
+        <v>-0.4167256090662874</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.603766895582406</v>
+        <v>2.575324034332799</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.933935207965332</v>
+        <v>-4.981339976714677</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8559961242644794</v>
+        <v>0.8370342167647413</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3693208403169426</v>
+        <v>-0.4167256090662874</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.608334127574194</v>
+        <v>2.579891266324587</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.044871460606581</v>
+        <v>-5.092276229355926</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7873636519691867</v>
+        <v>0.7684017444694486</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3693208403169426</v>
+        <v>-0.4167256090662874</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.584076156335401</v>
+        <v>2.555633295085794</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.053153534751639</v>
+        <v>-5.100558303500985</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7871822075310688</v>
+        <v>0.7682203000313308</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3776029144620009</v>
+        <v>-0.4250076832113458</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.582238297068272</v>
+        <v>2.553795435818665</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.895227935816346</v>
+        <v>-4.942632704565692</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8605248335373186</v>
+        <v>0.8415629260375805</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3776029144620009</v>
+        <v>-0.4250076832113458</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.592410683500404</v>
+        <v>2.563967822250797</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.808984472789969</v>
+        <v>-4.856389241539314</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8899684893217299</v>
+        <v>0.8710065818219919</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3776029144620009</v>
+        <v>-0.4250076832113458</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.587356954074264</v>
+        <v>2.558914092824657</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.854291292188949</v>
+        <v>-4.901696060938294</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8636215370066636</v>
+        <v>0.8446596295069255</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4184130774712317</v>
+        <v>-0.4658178462205766</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.554646631713251</v>
+        <v>2.526203770463645</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.88332439689125</v>
+        <v>-4.930729165640595</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8525601681588446</v>
+        <v>0.8335982606591066</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4184130774712317</v>
+        <v>-0.4658178462205766</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.555198504746353</v>
+        <v>2.526755643496746</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.79051391544039</v>
+        <v>-4.837918684189735</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8189570526305543</v>
+        <v>0.799995145130816</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3256025960203724</v>
+        <v>-0.3730073647697172</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.540157485508234</v>
+        <v>2.511714624258627</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.834903384769818</v>
+        <v>-4.882308153519163</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.803074740823384</v>
+        <v>0.784112833323646</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3699920653498001</v>
+        <v>-0.4173968340991449</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.515397279835179</v>
+        <v>2.486954418585571</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.722232166533567</v>
+        <v>-4.769636935282913</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.843218936629607</v>
+        <v>0.824257029129869</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2573208471135499</v>
+        <v>-0.3047256158628947</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.578075719288652</v>
+        <v>2.549632858039045</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.609855165350894</v>
+        <v>-4.65725993410024</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8936610329333434</v>
+        <v>0.8746991254336054</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2573208471135499</v>
+        <v>-0.3047256158628947</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.583567015119319</v>
+        <v>2.555124153869712</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.808089734237625</v>
+        <v>-4.85549450298697</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8258644071471903</v>
+        <v>0.8069024996474521</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4555554160002804</v>
+        <v>-0.5029601847496252</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.476123475555819</v>
+        <v>2.447680614306213</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.891091015262904</v>
+        <v>-4.938495784012249</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.631019614737732</v>
+        <v>0.6120577072379938</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4741263005274542</v>
+        <v>-0.5215310692767989</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.303336664840169</v>
+        <v>2.274893803590562</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.999705093706235</v>
+        <v>-5.047109862455581</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7077236440796051</v>
+        <v>0.6887617365798668</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4741263005274542</v>
+        <v>-0.5215310692767989</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.423486325559374</v>
+        <v>2.395043464309767</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.086303676687338</v>
+        <v>-5.133708445436683</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6875972369894869</v>
+        <v>0.6686353294897489</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4741263005274542</v>
+        <v>-0.5215310692767989</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.437999351661697</v>
+        <v>2.40955649041209</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.047920014129187</v>
+        <v>-5.095324782878532</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7003701433551162</v>
+        <v>0.6814082358553781</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.435742637969303</v>
+        <v>-0.4831474067186478</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.458448990538957</v>
+        <v>2.43000612928935</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.870803684094021</v>
+        <v>-4.918208452843366</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7679457042144844</v>
+        <v>0.7489837967147464</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.435742637969303</v>
+        <v>-0.4831474067186478</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.455178019384259</v>
+        <v>2.426735158134651</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.915895928927567</v>
+        <v>-4.963300697676912</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7505921980429793</v>
+        <v>0.731630290543241</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4976386811386928</v>
+        <v>-0.5450434498880375</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.418723785244538</v>
+        <v>2.390280923994931</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.736520507688799</v>
+        <v>-4.783925276438144</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8161293418449007</v>
+        <v>0.7971674343451625</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3408619229679741</v>
+        <v>-0.3882666917173189</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.506576815453383</v>
+        <v>2.478133954203777</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.781534721209406</v>
+        <v>-4.828939489958751</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7789311117682478</v>
+        <v>0.7599692042685096</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3712108182825787</v>
+        <v>-0.4186155870319235</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.46917493359621</v>
+        <v>2.440732072346603</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.048539231481841</v>
+        <v>-5.095944000231186</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6778208699982193</v>
+        <v>0.6588589624984813</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5655738563255273</v>
+        <v>-0.612978625074872</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.358248673109387</v>
+        <v>2.32980581185978</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.149737012919013</v>
+        <v>-5.197141781668359</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6365456793198518</v>
+        <v>0.6175837718201138</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6813874386201911</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.316407306878697</v>
+        <v>2.28796444562909</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.117261426748241</v>
+        <v>-5.164666195497587</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6471358753424776</v>
+        <v>0.6281739678427392</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6339826698708464</v>
+        <v>-0.6813874386201911</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.314007268433014</v>
+        <v>2.285564407183407</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.098223299040944</v>
+        <v>-5.145628067790289</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6512758456336414</v>
+        <v>0.6323139381339034</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.7395710499513857</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.275621820842542</v>
+        <v>2.247178959592935</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.129349930191562</v>
+        <v>-5.176754698940908</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8164070621120745</v>
+        <v>0.7974451546123364</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6921662812020409</v>
+        <v>-0.7395710499513857</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.453203689781223</v>
+        <v>2.424760828531615</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.181670310792354</v>
+        <v>-5.229075079541699</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7963122388578912</v>
+        <v>0.7773503313581531</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.7046241899425135</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.475005134772679</v>
+        <v>2.446562273523072</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.201927609321312</v>
+        <v>-5.249332378070657</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7942178498432342</v>
+        <v>0.7752559423434962</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6572194211931688</v>
+        <v>-0.7046241899425135</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.481013665169605</v>
+        <v>2.452570803919998</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.054184639086309</v>
+        <v>-5.101589407835655</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9324676857292569</v>
+        <v>0.9135057782295188</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.5368168327076304</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.660850727302557</v>
+        <v>2.63240786605295</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.156199321617531</v>
+        <v>-5.203604090366876</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8944554342482496</v>
+        <v>0.8754935267485116</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4894120639582856</v>
+        <v>-0.5368168327076304</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.663644348834038</v>
+        <v>2.635201487584431</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.150046615564746</v>
+        <v>-5.197451384314092</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8975788650610217</v>
+        <v>0.8786169575612837</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4832593579055013</v>
+        <v>-0.5306641266548461</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.667998320857367</v>
+        <v>2.63955545960776</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.292811948387397</v>
+        <v>-5.340216717136742</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8395532086720716</v>
+        <v>0.8205913011723336</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6734294594774964</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.581419597903887</v>
+        <v>2.55297673665428</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.230513949611274</v>
+        <v>-5.27791871836062</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9308079619793417</v>
+        <v>0.9118460544796037</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6260246907281517</v>
+        <v>-0.6734294594774964</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.647755151700708</v>
+        <v>2.619312290451101</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.028723751946116</v>
+        <v>-5.076128520695462</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.720104913434803</v>
+        <v>0.7011430059350645</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4280064985589973</v>
+        <v>-0.475411267308342</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.475146939391598</v>
+        <v>2.446704078141992</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.968833070303523</v>
+        <v>-5.016237839052868</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8143514184140153</v>
+        <v>0.7953895109142772</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3681158169164038</v>
+        <v>-0.4155205856657486</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.58137158069933</v>
+        <v>2.552928719449723</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.066573614928497</v>
+        <v>-5.113978383677843</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.789882936680069</v>
+        <v>0.770921029180331</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.384005095049384</v>
+        <v>-0.4314098637987288</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.586465749935585</v>
+        <v>2.558022888685978</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.037449223661643</v>
+        <v>-5.084853992410988</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8000686740114826</v>
+        <v>0.7811067665117446</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3548807037825291</v>
+        <v>-0.4022854725318738</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.60247636552037</v>
+        <v>2.574033504270763</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.036759851500419</v>
+        <v>-5.084164620249765</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7988360409159005</v>
+        <v>0.7798741334161625</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3548807037825291</v>
+        <v>-0.4022854725318738</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.600967983560298</v>
+        <v>2.572525122310692</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.043330816555012</v>
+        <v>-5.090735585304357</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7960705223294999</v>
+        <v>0.7771086148297615</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.361451668837122</v>
+        <v>-0.4088564375864667</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.596888271962979</v>
+        <v>2.568445410713372</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.03537684626024</v>
+        <v>-5.082781615009585</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7992521104474086</v>
+        <v>0.7802902029476706</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.361451668837122</v>
+        <v>-0.4088564375864667</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.596888271962979</v>
+        <v>2.568445410713372</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.025003469927153</v>
+        <v>-5.072408238676498</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8097832180084481</v>
+        <v>0.7908213105087101</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3510782925040347</v>
+        <v>-0.3984830612533795</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.609494054790636</v>
+        <v>2.581051193541029</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.897319160132857</v>
+        <v>-4.944723928882202</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8657493153008913</v>
+        <v>0.8467874078011532</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2233939827097383</v>
+        <v>-0.270798751459083</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.690997014041939</v>
+        <v>2.662554152792332</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.957985750535245</v>
+        <v>-5.005390519284591</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8282373516158081</v>
+        <v>0.8092754441160701</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3050922994282719</v>
+        <v>-0.3524970681776167</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.628732696486691</v>
+        <v>2.600289835237084</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.8929918906016</v>
+        <v>-4.940396659350945</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8583325981998948</v>
+        <v>0.8393706907001568</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2782616848241166</v>
+        <v>-0.3256664535734613</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.648928767859812</v>
+        <v>2.620485906610206</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.993750526358598</v>
+        <v>-5.041155295107943</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8221900835281737</v>
+        <v>0.8032281760284357</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.367087253551122</v>
+        <v>-0.4144920223004667</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.599794366254687</v>
+        <v>2.57135150500508</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.949547689272698</v>
+        <v>-4.996952458022043</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.845750820890371</v>
+        <v>0.826788913390633</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3228844164652215</v>
+        <v>-0.3702891852145663</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.632195671034065</v>
+        <v>2.603752809784458</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.98652671693614</v>
+        <v>-5.033931485685486</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8293692102942414</v>
+        <v>0.8104073027945033</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.285910514673891</v>
+        <v>-0.3333152834232357</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.652790012578111</v>
+        <v>2.624347151328504</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.006584795800981</v>
+        <v>-5.053989564550326</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8725937439313449</v>
+        <v>0.8536318364316067</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.285910514673891</v>
+        <v>-0.3333152834232357</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.70403777776115</v>
+        <v>2.675594916511543</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.96665412262309</v>
+        <v>-5.014058891372436</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8870067177967542</v>
+        <v>0.868044810297016</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2459798414960007</v>
+        <v>-0.2933846102453454</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.726436886262138</v>
+        <v>2.697994025012531</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.926183775060386</v>
+        <v>-4.973588543809731</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8981430850601062</v>
+        <v>0.879181177560368</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2055094939332957</v>
+        <v>-0.2529142626826404</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.745667323038031</v>
+        <v>2.717224461788423</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.86095959393318</v>
+        <v>-4.908364362682526</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9414201616036932</v>
+        <v>0.922458254103955</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1402853128060901</v>
+        <v>-0.1876900815554348</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.801989235807059</v>
+        <v>2.773546374557452</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.911453884290236</v>
+        <v>-4.958858653039582</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.917183417760151</v>
+        <v>0.898221510260413</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1853060499321643</v>
+        <v>-0.2327108186815091</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.770937765830694</v>
+        <v>2.742494904581088</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.931565540324945</v>
+        <v>-4.97897030907429</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9103955476775081</v>
+        <v>0.89143364017777</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1742787049347451</v>
+        <v>-0.2216834736840899</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.778810965160386</v>
+        <v>2.750368103910779</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.029246119597591</v>
+        <v>-5.076650888346936</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.03188108698966</v>
+        <v>1.012919179489922</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2849819002749339</v>
+        <v>-0.3323866690242787</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.872946818977484</v>
+        <v>2.844503957727877</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.896001767077581</v>
+        <v>3.586461132583541</v>
       </c>
       <c r="C1992" t="n">
         <v>3.270237721474783</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.029246119597591</v>
+        <v>-5.046744944723494</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.03188108698966</v>
+        <v>1.251183319271639</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.2849819002749339</v>
+        <v>-0.3024807254008362</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.263301518461151</v>
+        <v>3.088749286234282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240611.xlsx
+++ b/tame_output/ON/bt/strategyON_20240611.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.3%</t>
+          <t>452.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.2%</t>
+          <t>-687.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.8%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-1.5%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.1%</t>
+          <t>-278.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-157.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.2%</t>
+          <t>-272.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-137.1%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.815429559594854</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.7946149093366563</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.026463061801447</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.916035501734164</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.962955647600497</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8507317882173413</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.17398914980709</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.830413405252351</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.16721382293036</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9269218612306442</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.301628094421079</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.7593432356026</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30555468365612</v>
+        <v>-10.30902359713715</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9777756510365117</v>
+        <v>-0.9791632164289239</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.472906892066655</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.661058511499691</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23208485198867</v>
+        <v>-10.2355537654697</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9330160168761106</v>
+        <v>-0.9344035822685228</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.399437060399206</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.720512111993581</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40720926937521</v>
+        <v>-10.41067818285624</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9885105630832109</v>
+        <v>-0.9898981284756232</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.57456147778575</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.629992682309171</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.6416613633897</v>
+        <v>-10.64513027687073</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089510565590603</v>
+        <v>-1.090898130983015</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.57456147778575</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.622773517407575</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92946520792694</v>
+        <v>-10.93293412140797</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211304294179474</v>
+        <v>-1.212691859571887</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.862365322322988</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.443419019911256</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98225136352727</v>
+        <v>-10.9857202770083</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231302966581049</v>
+        <v>-1.232690531973462</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.958040808905385</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.387129517800374</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10828815689556</v>
+        <v>-11.11175707037659</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.27902395529925</v>
+        <v>-1.280411520691663</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.932789186095643</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.404974220115334</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05627264292674</v>
+        <v>-11.05974155640777</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254227414025324</v>
+        <v>-1.255614979417737</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.932789186095643</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.408964555801735</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19794448465086</v>
+        <v>-11.20141339813189</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312371377613713</v>
+        <v>-1.313758943006127</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.932789186095643</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.407489328902993</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14835364022603</v>
+        <v>-11.15182255370706</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277481629678908</v>
+        <v>-1.27886919507132</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.883198341670809</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.452297245722766</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13554624722125</v>
+        <v>-11.13901516070229</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285409806123681</v>
+        <v>-1.286797371516094</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.93205411667971</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.409932647070743</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90970109450184</v>
+        <v>-10.91317000798287</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185492671999709</v>
+        <v>-1.18688023739212</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.890127441092546</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.444667725459249</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78512243816425</v>
+        <v>-10.78859135164528</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134522064908613</v>
+        <v>-1.135909630301024</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.890127441092546</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.445806870015308</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83801772620854</v>
+        <v>-10.84148663968957</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153046405964219</v>
+        <v>-1.154433971356632</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.8851720950041</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.451413851830484</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.76588455092066</v>
+        <v>-10.76935346440169</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.118459431610431</v>
+        <v>-1.119846997002843</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.8851720950041</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.45714755606912</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.69451815831101</v>
+        <v>-10.69798707179204</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.099650136960437</v>
+        <v>-1.101037702352849</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.813805702394452</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.490230129241044</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.43068129110694</v>
+        <v>-10.43415020458797</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.003998871391717</v>
+        <v>-1.005386436784128</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.813805702394452</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.480346647928136</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.16343949023854</v>
+        <v>-10.16690840371957</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.898936711543731</v>
+        <v>-0.9003242769361433</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.813805702394452</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.478512087428763</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.06553245156205</v>
+        <v>-10.06900136504308</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8600742110465958</v>
+        <v>-0.861461776439008</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.745819952533895</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.519003222371636</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.04157891058609</v>
+        <v>-10.04504782406712</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8498242885107188</v>
+        <v>-0.851211853903131</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.721866411557938</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.534043853102704</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.777518972263298</v>
+        <v>-9.780987885744327</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7574606293433526</v>
+        <v>-0.7588481947357644</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.457806473235142</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.679219499934629</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.070439348758461</v>
+        <v>-9.07390826223949</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4774158136017186</v>
+        <v>-0.4788033789941304</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.457806473235142</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.676432466274328</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.03025505039227</v>
+        <v>-9.0337239638733</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.460998470367401</v>
+        <v>-0.4623860357598129</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.417622174868951</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.700886669181884</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.866855179452909</v>
+        <v>-8.870324092933938</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3962717007708996</v>
+        <v>-0.3976592661633109</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.250753390448559</v>
+        <v>-2.254222303929589</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.800374761054876</v>
+        <v>1.798293412966259</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.680778725972655</v>
+        <v>-8.636842870704339</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3139166905409452</v>
+        <v>-0.296342348433619</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.064676936968306</v>
+        <v>-2.02074108169999</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.919945061980881</v>
+        <v>1.94630657514187</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.53111233496514</v>
+        <v>-8.487176479696824</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2569423444508989</v>
+        <v>-0.2393680023435723</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.97177344572577</v>
+        <v>-1.927837590457454</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.972794946413443</v>
+        <v>1.999156459574432</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.398836861334253</v>
+        <v>-8.354901006065937</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.208664668251517</v>
+        <v>-0.1910903261441903</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.839497972094883</v>
+        <v>-1.795562116826567</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.047527717339002</v>
+        <v>2.073889230499992</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.208237186661099</v>
+        <v>-8.164301331392783</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1296097376946186</v>
+        <v>-0.1120353955872924</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.64889829742173</v>
+        <v>-1.604962442153415</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.164702582830531</v>
+        <v>2.19106409599152</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.959237387977518</v>
+        <v>-7.915301532709202</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01710347699752779</v>
+        <v>0.0004708651097988792</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.64889829742173</v>
+        <v>-1.604962442153415</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.177608924054189</v>
+        <v>2.203970437215179</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.064827377750623</v>
+        <v>-8.020891522482307</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.187315402505988</v>
+        <v>-0.1697410603986618</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.754488287194834</v>
+        <v>-1.710552431926519</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.986279000591108</v>
+        <v>2.012640513752098</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.08356227986922</v>
+        <v>-8.039626424600904</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1462650214763404</v>
+        <v>-0.1286906793690141</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.760084296854966</v>
+        <v>-1.71614844158665</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.031465736672116</v>
+        <v>2.057827249833105</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.935622238461621</v>
+        <v>-7.891686383193305</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2069679276014682</v>
+        <v>-0.189393585494142</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.739763380946408</v>
+        <v>-1.695827525678093</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.923779363529083</v>
+        <v>1.950140876690072</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.918464088330326</v>
+        <v>-7.87452823306201</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.208818653802429</v>
+        <v>-0.1912443116951024</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.722605230815114</v>
+        <v>-1.678669375546798</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.925360267354381</v>
+        <v>1.951721780515371</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.874915681559636</v>
+        <v>-7.83097982629132</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.198359903189246</v>
+        <v>-0.1807855610819193</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.722605230815114</v>
+        <v>-1.678669375546798</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.918399655259288</v>
+        <v>1.944761168420277</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.632767288105778</v>
+        <v>-7.588831432837462</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08703819142655966</v>
+        <v>-0.069463849319233</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.722605230815114</v>
+        <v>-1.678669375546798</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.932862009640431</v>
+        <v>1.959223522801421</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.524508150983256</v>
+        <v>-7.48057229571494</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.04920241611835596</v>
+        <v>-0.03162807401102929</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.722605230815114</v>
+        <v>-1.678669375546798</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.927394130099626</v>
+        <v>1.953755643260616</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.401217016166125</v>
+        <v>-7.357281160897809</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.0023878681809264</v>
+        <v>0.01518647392639982</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.599314095997983</v>
+        <v>-1.555378240729668</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.998866905000481</v>
+        <v>2.025228418161471</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.380067817262682</v>
+        <v>-7.336131961994366</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.01377278961777595</v>
+        <v>0.03134713172510217</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.57816489709454</v>
+        <v>-1.534229041826225</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.019257402579872</v>
+        <v>2.045618915740862</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.136302375279238</v>
+        <v>-7.092366520010922</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1070596747582044</v>
+        <v>0.1246340168655307</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.57816489709454</v>
+        <v>-1.534229041826225</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.015038110926923</v>
+        <v>2.041399624087912</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.034539555001943</v>
+        <v>-6.990603699733627</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1498891167891383</v>
+        <v>0.1674634588964645</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.564945828702111</v>
+        <v>-1.521009973433796</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.025093865882396</v>
+        <v>2.051455379043386</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.784689161052868</v>
+        <v>-6.740753305784552</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2425713493524704</v>
+        <v>0.2601456914597966</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.564945828702111</v>
+        <v>-1.521009973433796</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.017835940866099</v>
+        <v>2.044197454027088</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.608797068585435</v>
+        <v>-6.564861213317119</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.316527309860092</v>
+        <v>0.3341016519674187</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.564945828702111</v>
+        <v>-1.521009973433796</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.021435064386747</v>
+        <v>2.047796577547737</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.437350605562972</v>
+        <v>-6.393414750294656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3984334011236315</v>
+        <v>0.4160077432309577</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.393499365679648</v>
+        <v>-1.349563510411333</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.137630448254779</v>
+        <v>2.163991961415768</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.212317605894149</v>
+        <v>-6.168381750625833</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4874670786074575</v>
+        <v>0.5050414207147838</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.168466366010825</v>
+        <v>-1.12453051074251</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.27167072567237</v>
+        <v>2.298032238833359</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.148681863660214</v>
+        <v>-6.104746008391898</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5176161765553484</v>
+        <v>0.5351905186626751</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.104830623776891</v>
+        <v>-1.060894768508575</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.314546972067047</v>
+        <v>2.340908485228037</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.104919682354373</v>
+        <v>-6.060983827086057</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5163153078614808</v>
+        <v>0.5338896499688071</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.104830623776891</v>
+        <v>-1.060894768508575</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.295741230850843</v>
+        <v>2.322102744011832</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.864489185549512</v>
+        <v>-5.820553330281196</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6142305832083021</v>
+        <v>0.6318049253156288</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8644001269720305</v>
+        <v>-0.8204642717037149</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.441742605558637</v>
+        <v>2.468104118719626</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.792246617378318</v>
+        <v>-5.748310762110002</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6470569243116002</v>
+        <v>0.6646312664189269</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8644001269720305</v>
+        <v>-0.8204642717037149</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.445671919393457</v>
+        <v>2.472033432554446</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.73924829509693</v>
+        <v>-5.695312439828614</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6689348371414954</v>
+        <v>0.686509179248822</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8090638679700917</v>
+        <v>-0.7651280127017761</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.47955225871196</v>
+        <v>2.505913771872949</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.630443409617203</v>
+        <v>-5.586507554348887</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7094548625533799</v>
+        <v>0.7270292046607061</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8090638679700917</v>
+        <v>-0.7651280127017761</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.476550329931953</v>
+        <v>2.502911843092943</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.410422611580192</v>
+        <v>-5.366486756311876</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7990422187787982</v>
+        <v>0.8166165608861244</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6678440229021114</v>
+        <v>-0.6239081676337959</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.562861273983356</v>
+        <v>2.589222787144345</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.277554922516915</v>
+        <v>-5.233619067248599</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8680834772059325</v>
+        <v>0.8856578193132592</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6678440229021114</v>
+        <v>-0.6239081676337959</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.578755456785179</v>
+        <v>2.605116969946168</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.118039818997545</v>
+        <v>-5.074103963729229</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9330353630539823</v>
+        <v>0.9506097051613089</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5083289193827415</v>
+        <v>-0.4643930641144259</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.675610363337103</v>
+        <v>2.701971876498092</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.973367673897807</v>
+        <v>-4.929431818629491</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.000992323655317</v>
+        <v>1.018566665762644</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3636567742830041</v>
+        <v>-0.3197209190146885</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.772501752958386</v>
+        <v>2.798863266119374</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.0332425012555</v>
+        <v>-4.989306645987184</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9630798841136663</v>
+        <v>0.9806542262209925</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4235316016406962</v>
+        <v>-0.3795957463723806</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.722614347945196</v>
+        <v>2.748975861106185</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.946443003476491</v>
+        <v>-4.902507148208175</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.020200176547836</v>
+        <v>1.037774518655162</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4235316016406962</v>
+        <v>-0.3795957463723806</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.745014841267762</v>
+        <v>2.771376354428751</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.948912709938297</v>
+        <v>-4.904976854669981</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.019284695336526</v>
+        <v>1.036859037443852</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4260013081025024</v>
+        <v>-0.3820654528341868</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.743605418764091</v>
+        <v>2.76996693192508</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.017282896262307</v>
+        <v>-4.973347040993991</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.002943543281623</v>
+        <v>1.02051788538895</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4167256090662874</v>
+        <v>-0.3727897537979719</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.760177760660521</v>
+        <v>2.786539273821511</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.125821077178441</v>
+        <v>-5.081885221910125</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9499649795470613</v>
+        <v>0.9675393216543875</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4167256090662874</v>
+        <v>-0.3727897537979719</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.750614469292413</v>
+        <v>2.776975982453402</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.156814236507146</v>
+        <v>-5.11287838123883</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7622772808559661</v>
+        <v>0.7798516229632924</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4167256090662874</v>
+        <v>-0.3727897537979719</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.575324034332799</v>
+        <v>2.601685547493789</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.981339976714677</v>
+        <v>-4.937404121446361</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8370342167647413</v>
+        <v>0.8546085588720675</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4167256090662874</v>
+        <v>-0.3727897537979719</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.579891266324587</v>
+        <v>2.606252779485577</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.092276229355926</v>
+        <v>-5.04834037408761</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7684017444694486</v>
+        <v>0.7859760865767753</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4167256090662874</v>
+        <v>-0.3727897537979719</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.555633295085794</v>
+        <v>2.581994808246784</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.100558303500985</v>
+        <v>-5.056622448232669</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7682203000313308</v>
+        <v>0.7857946421386575</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4250076832113458</v>
+        <v>-0.3810718279430302</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.553795435818665</v>
+        <v>2.580156948979654</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.942632704565692</v>
+        <v>-4.898696849297376</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8415629260375805</v>
+        <v>0.8591372681449068</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4250076832113458</v>
+        <v>-0.3810718279430302</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.563967822250797</v>
+        <v>2.590329335411786</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.856389241539314</v>
+        <v>-4.812453386270998</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8710065818219919</v>
+        <v>0.8885809239293183</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4250076832113458</v>
+        <v>-0.3810718279430302</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.558914092824657</v>
+        <v>2.585275605985647</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.901696060938294</v>
+        <v>-4.857760205669978</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8446596295069255</v>
+        <v>0.862233971614252</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4658178462205766</v>
+        <v>-0.421881990952261</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.526203770463645</v>
+        <v>2.552565283624634</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.930729165640595</v>
+        <v>-4.886793310372279</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8335982606591066</v>
+        <v>0.851172602766433</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4658178462205766</v>
+        <v>-0.421881990952261</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.526755643496746</v>
+        <v>2.553117156657736</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.837918684189735</v>
+        <v>-4.793982828921419</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.799995145130816</v>
+        <v>0.8175694872381425</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3730073647697172</v>
+        <v>-0.3290715095014017</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.511714624258627</v>
+        <v>2.538076137419617</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.882308153519163</v>
+        <v>-4.838372298250847</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.784112833323646</v>
+        <v>0.8016871754309722</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4173968340991449</v>
+        <v>-0.3734609788308293</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.486954418585571</v>
+        <v>2.513315931746561</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.769636935282913</v>
+        <v>-4.725701080014597</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.824257029129869</v>
+        <v>0.8418313712371954</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3047256158628947</v>
+        <v>-0.2607897605945791</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.549632858039045</v>
+        <v>2.575994371200034</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.65725993410024</v>
+        <v>-4.613324078831924</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8746991254336054</v>
+        <v>0.8922734675409318</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3047256158628947</v>
+        <v>-0.2607897605945791</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.555124153869712</v>
+        <v>2.581485667030701</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.85549450298697</v>
+        <v>-4.811558647718654</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8069024996474521</v>
+        <v>0.8244768417547785</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5029601847496252</v>
+        <v>-0.4590243294813097</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.447680614306213</v>
+        <v>2.474042127467202</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.938495784012249</v>
+        <v>-4.894559928743933</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6120577072379938</v>
+        <v>0.6296320493453202</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5215310692767989</v>
+        <v>-0.4775952140084835</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.274893803590562</v>
+        <v>2.301255316751551</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.047109862455581</v>
+        <v>-5.003174007187265</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6887617365798668</v>
+        <v>0.7063360786871935</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5215310692767989</v>
+        <v>-0.4775952140084835</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.395043464309767</v>
+        <v>2.421404977470757</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.133708445436683</v>
+        <v>-5.089772590168367</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6686353294897489</v>
+        <v>0.6862096715970751</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5215310692767989</v>
+        <v>-0.4775952140084835</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.40955649041209</v>
+        <v>2.43591800357308</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.095324782878532</v>
+        <v>-5.051388927610216</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6814082358553781</v>
+        <v>0.6989825779627044</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4831474067186478</v>
+        <v>-0.4392115514503323</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.43000612928935</v>
+        <v>2.456367642450339</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.918208452843366</v>
+        <v>-4.87427259757505</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7489837967147464</v>
+        <v>0.7665581388220728</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4831474067186478</v>
+        <v>-0.4392115514503323</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.426735158134651</v>
+        <v>2.453096671295641</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.963300697676912</v>
+        <v>-4.919364842408596</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.731630290543241</v>
+        <v>0.7492046326505675</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5450434498880375</v>
+        <v>-0.5011075946197221</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.390280923994931</v>
+        <v>2.41664243715592</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.783925276438144</v>
+        <v>-4.739989421169828</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7971674343451625</v>
+        <v>0.8147417764524889</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3882666917173189</v>
+        <v>-0.3443308364490034</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.478133954203777</v>
+        <v>2.504495467364766</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.828939489958751</v>
+        <v>-4.785003634690435</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7599692042685096</v>
+        <v>0.777543546375836</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4186155870319235</v>
+        <v>-0.374679731763608</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.440732072346603</v>
+        <v>2.467093585507593</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.095944000231186</v>
+        <v>-5.05200814496287</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6588589624984813</v>
+        <v>0.676433304605808</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.612978625074872</v>
+        <v>-0.5690427698065565</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.32980581185978</v>
+        <v>2.35616732502077</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.197141781668359</v>
+        <v>-5.153205926400043</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6175837718201138</v>
+        <v>0.63515811392744</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6813874386201911</v>
+        <v>-0.6374515833518757</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.28796444562909</v>
+        <v>2.31432595879008</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.164666195497587</v>
+        <v>-5.120730340229271</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6281739678427392</v>
+        <v>0.6457483099500658</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6813874386201911</v>
+        <v>-0.6374515833518757</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.285564407183407</v>
+        <v>2.311925920344396</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.145628067790289</v>
+        <v>-5.101692212521973</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6323139381339034</v>
+        <v>0.6498882802412296</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7395710499513857</v>
+        <v>-0.6956351946830702</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.247178959592935</v>
+        <v>2.273540472753924</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.176754698940908</v>
+        <v>-5.132818843672592</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7974451546123364</v>
+        <v>0.8150194967196627</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7395710499513857</v>
+        <v>-0.6956351946830702</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.424760828531615</v>
+        <v>2.451122341692605</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.229075079541699</v>
+        <v>-5.185139224273383</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7773503313581531</v>
+        <v>0.7949246734654798</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7046241899425135</v>
+        <v>-0.6606883346741981</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.446562273523072</v>
+        <v>2.472923786684062</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.249332378070657</v>
+        <v>-5.205396522802341</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7752559423434962</v>
+        <v>0.7928302844508224</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7046241899425135</v>
+        <v>-0.6606883346741981</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.452570803919998</v>
+        <v>2.478932317080988</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.101589407835655</v>
+        <v>-5.057653552567339</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9135057782295188</v>
+        <v>0.9310801203368455</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5368168327076304</v>
+        <v>-0.4928809774393149</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.63240786605295</v>
+        <v>2.658769379213939</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.203604090366876</v>
+        <v>-5.15966823509856</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8754935267485116</v>
+        <v>0.8930678688558378</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5368168327076304</v>
+        <v>-0.4928809774393149</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.635201487584431</v>
+        <v>2.66156300074542</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.197451384314092</v>
+        <v>-5.153515529045776</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8786169575612837</v>
+        <v>0.8961912996686099</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5306641266548461</v>
+        <v>-0.4867282713865306</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.63955545960776</v>
+        <v>2.665916972768749</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.989651210724281</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.340216717136742</v>
+        <v>-5.296280861868426</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8205913011723336</v>
+        <v>0.8707824416631631</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6734294594774964</v>
+        <v>-0.629493604209181</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.55297673665428</v>
+        <v>2.611955048198772</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.055986764521101</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.27791871836062</v>
+        <v>-5.233982863092304</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9118460544796037</v>
+        <v>0.9620371949704327</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6734294594774964</v>
+        <v>-0.629493604209181</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.619312290451101</v>
+        <v>2.678290601995593</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.764567636910499</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.076128520695462</v>
+        <v>-5.032192665427146</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7011430059350645</v>
+        <v>0.751334146425894</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.475411267308342</v>
+        <v>-0.4314754120400266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.446704078141992</v>
+        <v>2.505682389686484</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.834857869232675</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.016237839052868</v>
+        <v>-4.972301983784552</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7953895109142772</v>
+        <v>0.8455806514051065</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4155205856657486</v>
+        <v>-0.3715847303974331</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.552928719449723</v>
+        <v>2.611907030994215</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.849485605348718</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.113978383677843</v>
+        <v>-5.070042528409527</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.770921029180331</v>
+        <v>0.8211121696711605</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4314098637987288</v>
+        <v>-0.3874740085304133</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.558022888685978</v>
+        <v>2.617001200230471</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.84802158617339</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.084853992410988</v>
+        <v>-5.246380288532456</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7811067665117446</v>
+        <v>0.7491130464466602</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4022854725318738</v>
+        <v>-0.5638117686533427</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.574033504270763</v>
+        <v>2.509734524981384</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.846513204213319</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.084164620249765</v>
+        <v>-5.245690916371233</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7798741334161625</v>
+        <v>0.7478804133510781</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4022854725318738</v>
+        <v>-0.5638117686533427</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.572525122310692</v>
+        <v>2.508226143021313</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.846376071648755</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.090735585304357</v>
+        <v>-5.252261881425826</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7771086148297615</v>
+        <v>0.7451148947646771</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4088564375864667</v>
+        <v>-0.5703827337079357</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.568445410713372</v>
+        <v>2.504146431423993</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.846376071648755</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.082781615009585</v>
+        <v>-5.244307911131053</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7802902029476706</v>
+        <v>0.7482964828825862</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4088564375864667</v>
+        <v>-0.5703827337079357</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.568445410713372</v>
+        <v>2.504146431423993</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.852757828676559</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.072408238676498</v>
+        <v>-5.233934534797966</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7908213105087101</v>
+        <v>0.7588275904436252</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3984830612533795</v>
+        <v>-0.5600093573748484</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.581051193541029</v>
+        <v>2.51675221425165</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.857650202051284</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.944723928882202</v>
+        <v>-5.10625022500367</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8467874078011532</v>
+        <v>0.8147936877360684</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.270798751459083</v>
+        <v>-0.4323250475805519</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.662554152792332</v>
+        <v>2.598255173502953</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.844404874527156</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.005390519284591</v>
+        <v>-5.16691681540606</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8092754441160701</v>
+        <v>0.7772817240509848</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3524970681776167</v>
+        <v>-0.5140233642990856</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.600289835237084</v>
+        <v>2.535990855947705</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.848502577137785</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.940396659350945</v>
+        <v>-5.101922955472414</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8393706907001568</v>
+        <v>0.8073769706350715</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3256664535734613</v>
+        <v>-0.4871927496949302</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.620485906610206</v>
+        <v>2.556186927320827</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.852663516768863</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.041155295107943</v>
+        <v>-5.202681591229412</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8032281760284357</v>
+        <v>0.7712344559633504</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4144920223004667</v>
+        <v>-0.5760183184219356</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.57135150500508</v>
+        <v>2.507052525715701</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.8585431192967</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.996952458022043</v>
+        <v>-5.158478754143512</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.826788913390633</v>
+        <v>0.7947951933255477</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3702891852145663</v>
+        <v>-0.5318154813360352</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.603752809784458</v>
+        <v>2.539453830495079</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.856953119765947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.033931485685486</v>
+        <v>-5.195457781806955</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8104073027945033</v>
+        <v>0.7784135827294181</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3333152834232357</v>
+        <v>-0.4948415795447046</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.624347151328504</v>
+        <v>2.560048172039125</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.908200884948987</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.053989564550326</v>
+        <v>-5.215515860671795</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8536318364316067</v>
+        <v>0.8216381163665214</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3333152834232357</v>
+        <v>-0.4948415795447046</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.675594916511543</v>
+        <v>2.611295937222164</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.90664158954324</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.014058891372436</v>
+        <v>-5.175585187493905</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.868044810297016</v>
+        <v>0.8360510902319307</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2933846102453454</v>
+        <v>-0.4549109063668143</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.697994025012531</v>
+        <v>2.633695045723152</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.90158981778151</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.973588543809731</v>
+        <v>-5.1351148399312</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.879181177560368</v>
+        <v>0.8471874574952829</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2529142626826404</v>
+        <v>-0.4144405588041093</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.717224461788423</v>
+        <v>2.652925482499045</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.918777221874215</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.908364362682526</v>
+        <v>-5.069890658803994</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.922458254103955</v>
+        <v>0.8904645340388697</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1876900815554348</v>
+        <v>-0.3492163776769037</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.773546374557452</v>
+        <v>2.709247395268073</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.914738194173495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.958858653039582</v>
+        <v>-5.120384949161051</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.898221510260413</v>
+        <v>0.8662277901953277</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2327108186815091</v>
+        <v>-0.394237114802978</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.742494904581088</v>
+        <v>2.678195925291709</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.915994986504736</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.97897030907429</v>
+        <v>-5.140496605195759</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.89143364017777</v>
+        <v>0.8594399201126848</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2216834736840899</v>
+        <v>-0.3832097698055588</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.750368103910779</v>
+        <v>2.686069124621401</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393544</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.076552757525946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.076650888346936</v>
+        <v>-5.238177184468405</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.012919179489922</v>
+        <v>0.9809254594248369</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3323866690242787</v>
+        <v>-0.4939129651457476</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.844503957727877</v>
+        <v>2.780204978438498</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.586461132583541</v>
+        <v>3.795096181660428</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.270237721474783</v>
+        <v>3.081175719827345</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.046744944723494</v>
+        <v>-5.259677601533204</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.251183319271639</v>
+        <v>0.9769482549003161</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3024807254008362</v>
+        <v>-0.4848535759118556</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.088749286234282</v>
+        <v>2.790263574280232</v>
       </c>
     </row>
   </sheetData>
